--- a/NVIDIA/NVIDIA_model.xlsx
+++ b/NVIDIA/NVIDIA_model.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\Folders\Job Application\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90E0FFFE-7EB9-43DC-BF40-7CA9A8B0C968}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7398D3C7-F175-497A-B881-D945FCDD0B16}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8364" xr2:uid="{DEFB8350-6F8A-4703-96BD-193C79891CE3}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="55">
   <si>
     <t>Projected</t>
   </si>
@@ -187,6 +187,9 @@
   </si>
   <si>
     <t>EBITDA</t>
+  </si>
+  <si>
+    <t>Yasen Georgiev</t>
   </si>
 </sst>
 </file>
@@ -208,7 +211,7 @@
     <numFmt numFmtId="174" formatCode="0.0;\(0.0\);&quot;-&quot;"/>
     <numFmt numFmtId="175" formatCode="\$\ 0.00"/>
   </numFmts>
-  <fonts count="39" x14ac:knownFonts="1">
+  <fonts count="40" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -479,6 +482,14 @@
       <family val="2"/>
       <charset val="204"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -580,7 +591,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="141">
+  <cellXfs count="142">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
@@ -792,6 +803,7 @@
     <xf numFmtId="164" fontId="13" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -1107,7 +1119,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5AC01A37-A80F-4D3D-AD90-98F8D6A4045F}">
-  <dimension ref="B2:Q133"/>
+  <dimension ref="B2:Y1005"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="14.77734375" customWidth="1"/>
@@ -3921,6 +3933,11 @@
       <c r="O133" s="100"/>
       <c r="P133" s="100"/>
     </row>
+    <row r="1005" spans="25:25" x14ac:dyDescent="0.3">
+      <c r="Y1005" s="141" t="s">
+        <v>54</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="L63:P63"/>
